--- a/outputs/51680.xlsx
+++ b/outputs/51680.xlsx
@@ -52,16 +52,16 @@
     <t xml:space="preserve">Black White, Orange</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue, Green, Red Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green, Red Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue, Black White, Green, Red Purple, Orange, Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue, Green, Orange, Brown</t>
+    <t xml:space="preserve">Blue, Green , Red Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green , Red Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue, Black White, Green , Red Purple, Orange, Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue, Green , Orange, Brown</t>
   </si>
 </sst>
 </file>
